--- a/data/downloads/NE/Ambulatory%20Surgical%20Center%20Rates%20July%201%202022.xlsx
+++ b/data/downloads/NE/Ambulatory%20Surgical%20Center%20Rates%20July%201%202022.xlsx
@@ -74455,7 +74455,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932EA8AC-CFD5-4ACF-806A-9068A4B1E984}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EF06E-8FFD-45CE-84FD-6F4616280225}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/downloads/NE/Ambulatory%20Surgical%20Center%20Rates%20July%201%202022.xlsx
+++ b/data/downloads/NE/Ambulatory%20Surgical%20Center%20Rates%20July%201%202022.xlsx
@@ -74455,7 +74455,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EF06E-8FFD-45CE-84FD-6F4616280225}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95D66796-D196-42CA-86A8-CCC10C64298F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
